--- a/65_Threshold_OUTPUT/direct_Q92PW3_Sinorhizobium_meliloti_1021.xlsx
+++ b/65_Threshold_OUTPUT/direct_Q92PW3_Sinorhizobium_meliloti_1021.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TGTTCTTGATTTGTTC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TGTTC</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;TTGATT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.004398240703718513</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>GATTTGTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>GTT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>GAT</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;TT&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.4958016793282687</v>
       </c>
     </row>
@@ -535,7 +565,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTCTTGATT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -543,7 +573,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;CTTGA&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.8556577369052379</v>
       </c>
     </row>
@@ -564,7 +604,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTCTTGATTT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -572,7 +612,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;CTTGAT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.8556577369052379</v>
       </c>
     </row>
@@ -593,7 +643,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -601,7 +651,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9846061575369852</v>
       </c>
     </row>
@@ -622,7 +682,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTTGTT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -630,7 +690,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;TG&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9690123950419832</v>
       </c>
     </row>
@@ -651,7 +721,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -659,7 +729,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;G&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.8980407836865254</v>
       </c>
     </row>
